--- a/AAII_Financials/Quarterly/WTFC_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/WTFC_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="92">
   <si>
     <t>WTFC</t>
   </si>
@@ -656,299 +656,306 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AP102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="42" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="43" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43738</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43646</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43555</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43465</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43373</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43190</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43100</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>43008</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42916</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42825</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42735</v>
       </c>
-      <c r="AP7" s="2">
+      <c r="AQ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>714400</v>
+      </c>
+      <c r="E8" s="3">
         <v>682800</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>686100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>675600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>648100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>618400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>621100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>592900</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>551300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>582700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>527700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>554500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>531900</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>542400</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>580700</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>466500</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>372000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>328300</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>328000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>322500</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>319600</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>305500</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>308000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>311200</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>329800</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>344100</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>349700</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>354600</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>346800</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>334000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>320600</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>305000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>284000</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>261200</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>251800</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>247700</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>231200</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>215800</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>215000</v>
       </c>
-      <c r="AP8" s="3">
+      <c r="AQ8" s="3">
         <v>208100</v>
       </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -1069,53 +1076,56 @@
       <c r="AP9" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AQ9" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>714400</v>
+      </c>
+      <c r="E10" s="3">
         <v>682800</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>686100</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>675600</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>648100</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>618400</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>621100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>592900</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>551300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>582700</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>527700</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>554500</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>531900</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>542400</v>
       </c>
-      <c r="Q10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R10" s="3" t="s">
         <v>5</v>
       </c>
@@ -1191,8 +1201,11 @@
       <c r="AP10" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AQ10" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1235,8 +1248,9 @@
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1357,8 +1371,11 @@
       <c r="AP12" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AQ12" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1479,53 +1496,56 @@
       <c r="AP13" s="3">
         <v>0</v>
       </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="E14" s="3">
         <v>-800</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-600</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-500</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-400</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-800</v>
-      </c>
-      <c r="I14" s="3">
-        <v>-500</v>
       </c>
       <c r="J14" s="3">
         <v>-500</v>
       </c>
       <c r="K14" s="3">
-        <v>-400</v>
+        <v>-500</v>
       </c>
       <c r="L14" s="3">
         <v>-400</v>
       </c>
       <c r="M14" s="3">
+        <v>-400</v>
+      </c>
+      <c r="N14" s="3">
         <v>-200</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>-500</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>-200</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>-400</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
       <c r="R14" s="3">
         <v>0</v>
       </c>
@@ -1601,79 +1621,82 @@
       <c r="AP14" s="3">
         <v>0</v>
       </c>
+      <c r="AQ14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>18000</v>
+      </c>
+      <c r="E15" s="3">
         <v>18900</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>18800</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>18100</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>20100</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>19000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>18900</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>15200</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>12800</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>10800</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>11500</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>15600</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>6400</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>9000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>-11500</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>-10900</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>-10400</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>-11300</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>-12000</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>-11900</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>-12000</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>-12800</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>-12600</v>
-      </c>
-      <c r="Z15" s="3">
-        <v>-12100</v>
       </c>
       <c r="AA15" s="3">
         <v>-12100</v>
@@ -1682,49 +1705,52 @@
         <v>-12100</v>
       </c>
       <c r="AC15" s="3">
+        <v>-12100</v>
+      </c>
+      <c r="AD15" s="3">
         <v>-12800</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>-11800</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>-11700</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>-11300</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>-9900</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>-8500</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>-7900</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>-7500</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AL15" s="3">
         <v>-8000</v>
       </c>
-      <c r="AL15" s="3">
+      <c r="AM15" s="3">
         <v>-7900</v>
       </c>
-      <c r="AM15" s="3">
+      <c r="AN15" s="3">
         <v>-6800</v>
       </c>
-      <c r="AN15" s="3">
+      <c r="AO15" s="3">
         <v>-5800</v>
       </c>
-      <c r="AO15" s="3">
+      <c r="AP15" s="3">
         <v>-5400</v>
       </c>
-      <c r="AP15" s="3">
+      <c r="AQ15" s="3">
         <v>-4700</v>
       </c>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1764,252 +1790,259 @@
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>385200</v>
+      </c>
+      <c r="E17" s="3">
         <v>366500</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>366700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>363200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>364400</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>348900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>351700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>347100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>329100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>317100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>319200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>318800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>310000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>289500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>171600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>71500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>54600</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>33100</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>41300</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>27000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>24700</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>-1800</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>48600</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>55200</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>66700</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>82600</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>95700</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>100600</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>105200</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>82600</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>76900</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>68400</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>50900</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>44500</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>40500</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>39600</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>35700</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>28400</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>31600</v>
       </c>
-      <c r="AP17" s="3">
+      <c r="AQ17" s="3">
         <v>33100</v>
       </c>
     </row>
-    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>329300</v>
+      </c>
+      <c r="E18" s="3">
         <v>316300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>319400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>312400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>283700</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>269500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>269400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>245800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>222200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>265600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>208600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>235700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>221900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>252900</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>409100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>395100</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>317400</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>295200</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>286700</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>295500</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>294900</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>307300</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>259400</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>256000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>263100</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>261500</v>
-      </c>
-      <c r="AC18" s="3">
-        <v>254000</v>
       </c>
       <c r="AD18" s="3">
         <v>254000</v>
       </c>
       <c r="AE18" s="3">
+        <v>254000</v>
+      </c>
+      <c r="AF18" s="3">
         <v>241600</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>251400</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>243700</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>236600</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>233100</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>216700</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>211300</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>208100</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>195500</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>187400</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>183400</v>
       </c>
-      <c r="AP18" s="3">
+      <c r="AQ18" s="3">
         <v>175000</v>
       </c>
     </row>
-    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2052,252 +2085,259 @@
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>12300</v>
+      </c>
+      <c r="E20" s="3">
         <v>16200</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>17700</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>16900</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>17100</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>17200</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>16800</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>13600</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>11300</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>16100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>43500</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>11300</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>10600</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>9700</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-214000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-195000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-185800</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-121600</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-149700</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-145700</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-150800</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-100400</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-124700</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-118700</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-232400</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-174400</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-137300</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-119400</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-131400</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-132700</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-136000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-113700</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-111500</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>-108700</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>-115500</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>-103900</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>-93600</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>-99400</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AP20" s="3">
         <v>-95100</v>
       </c>
-      <c r="AP20" s="3">
+      <c r="AQ20" s="3">
         <v>-90000</v>
       </c>
     </row>
-    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>335000</v>
+      </c>
+      <c r="E21" s="3">
         <v>319100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>320500</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>313700</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>286800</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>271300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>271500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>247400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>223800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>260300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>176600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>240000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>217600</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>252200</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>212500</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>219600</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>152300</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>198200</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>163500</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>173600</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>170100</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>232400</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>159800</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>161400</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>54500</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>110500</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>140200</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>156100</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>132300</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>139800</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>126400</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>139700</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>137700</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>123900</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>112400</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>120800</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>117500</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>102500</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>102700</v>
       </c>
-      <c r="AP21" s="3">
+      <c r="AQ21" s="3">
         <v>96600</v>
       </c>
     </row>
-    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2340,8 +2380,8 @@
       <c r="P22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q22" s="3">
-        <v>0</v>
+      <c r="Q22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R22" s="3">
         <v>0</v>
@@ -2418,252 +2458,261 @@
       <c r="AP22" s="3">
         <v>0</v>
       </c>
+      <c r="AQ22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>318000</v>
+      </c>
+      <c r="E23" s="3">
         <v>300900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>302200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>296000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>267100</v>
-      </c>
-      <c r="H23" s="3">
-        <v>253100</v>
       </c>
       <c r="I23" s="3">
         <v>253100</v>
       </c>
       <c r="J23" s="3">
+        <v>253100</v>
+      </c>
+      <c r="K23" s="3">
         <v>232700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>211300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>250000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>165200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>224900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>211400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>243600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>195200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>200000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>131700</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>173700</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>137000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>149700</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>144200</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>206900</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>134700</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>137300</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>30700</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>87100</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>116700</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>134600</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>110200</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>118600</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>107700</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>122800</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>121600</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>108100</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>95800</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>104200</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>101900</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>88000</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>88300</v>
       </c>
-      <c r="AP23" s="3">
+      <c r="AQ23" s="3">
         <v>85100</v>
       </c>
     </row>
-    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>84300</v>
+      </c>
+      <c r="E24" s="3">
         <v>73600</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>79200</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>79800</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>71600</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>64000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>67700</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>62700</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>59000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>62700</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>41800</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>60700</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>56700</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>63400</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>50400</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>57100</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>37100</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>46300</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>38300</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>40600</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>39000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>53700</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>33500</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>30000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>9000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>24300</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>30700</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>35500</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>28700</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>29500</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>29200</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>30900</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>32000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>26100</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>34600</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>38600</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>37000</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>29600</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>33700</v>
       </c>
-      <c r="AP24" s="3">
+      <c r="AQ24" s="3">
         <v>31900</v>
       </c>
     </row>
-    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2784,252 +2833,261 @@
       <c r="AP25" s="3">
         <v>0</v>
       </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>233700</v>
+      </c>
+      <c r="E26" s="3">
         <v>227400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>223000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>216300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>195500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>189000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>185400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>170000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>152400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>187300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>123500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>164200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>154800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>180200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>144800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>143000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>94500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>127400</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>98800</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>109100</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>105100</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>153100</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>101200</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>107300</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>21700</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>62800</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>86000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>99100</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>81500</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>89100</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>78400</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>91900</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>89600</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>82000</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>61200</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>65600</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>64900</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>58400</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>54600</v>
       </c>
-      <c r="AP26" s="3">
+      <c r="AQ26" s="3">
         <v>53100</v>
       </c>
     </row>
-    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>225300</v>
+      </c>
+      <c r="E27" s="3">
         <v>219000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>214700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>188900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>188500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>182000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>178400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>163000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>145400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>180300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>116500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>157200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>147800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>173200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>137800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>136000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>87500</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>120400</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>91800</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>102100</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>98100</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>146200</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>94200</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>97000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>19600</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>60800</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>83900</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>97100</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>79400</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>87100</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>76400</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>89900</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>87500</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>79900</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>59200</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>63600</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>62800</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>54800</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>51000</v>
       </c>
-      <c r="AP27" s="3">
+      <c r="AQ27" s="3">
         <v>49500</v>
       </c>
     </row>
-    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3150,8 +3208,11 @@
       <c r="AP28" s="3">
         <v>0</v>
       </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3224,17 +3285,17 @@
       <c r="Z29" s="3">
         <v>0</v>
       </c>
-      <c r="AA29" s="3" t="s">
-        <v>5</v>
+      <c r="AA29" s="3">
+        <v>0</v>
       </c>
       <c r="AB29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AC29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD29" s="3" t="s">
-        <v>5</v>
+      <c r="AC29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD29" s="3">
+        <v>0</v>
       </c>
       <c r="AE29" s="3" t="s">
         <v>5</v>
@@ -3242,24 +3303,24 @@
       <c r="AF29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AG29" s="3">
+      <c r="AG29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH29" s="3">
         <v>1200</v>
       </c>
-      <c r="AH29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AI29" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AJ29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AK29" s="3">
+      <c r="AK29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL29" s="3">
         <v>7600</v>
       </c>
-      <c r="AL29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AM29" s="3" t="s">
         <v>5</v>
       </c>
@@ -3272,8 +3333,11 @@
       <c r="AP29" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AQ29" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3394,8 +3458,11 @@
       <c r="AP30" s="3">
         <v>0</v>
       </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3516,252 +3583,261 @@
       <c r="AP31" s="3">
         <v>0</v>
       </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-12300</v>
+      </c>
+      <c r="E32" s="3">
         <v>-16200</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-17700</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-16900</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-17100</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-17200</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-16800</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-13600</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-11300</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-16100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-43500</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-11300</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-10600</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-9700</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>214000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>195000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>185800</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>121600</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>149700</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>145700</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>150800</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>100400</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>124700</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>118700</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>232400</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>174400</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>137300</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>119400</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>131400</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>132700</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>136000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>113700</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>111500</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>108700</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>115500</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>103900</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>93600</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>99400</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AP32" s="3">
         <v>95100</v>
       </c>
-      <c r="AP32" s="3">
+      <c r="AQ32" s="3">
         <v>90000</v>
       </c>
     </row>
-    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>233700</v>
+      </c>
+      <c r="E33" s="3">
         <v>227400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>223000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>216300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>195500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>189000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>185400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>170000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>152400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>187300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>123500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>164200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>154800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>180200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>137800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>136000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>87500</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>120400</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>91800</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>102100</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>98100</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>146200</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>94200</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>97000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>19600</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>60800</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>83900</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>97100</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>79400</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>87100</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>77600</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>89900</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>87500</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>79900</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>66700</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>63600</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>62800</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>54800</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>51000</v>
       </c>
-      <c r="AP33" s="3">
+      <c r="AQ33" s="3">
         <v>49500</v>
       </c>
     </row>
-    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3882,257 +3958,266 @@
       <c r="AP34" s="3">
         <v>0</v>
       </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>233700</v>
+      </c>
+      <c r="E35" s="3">
         <v>227400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>223000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>216300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>195500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>189000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>185400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>170000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>152400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>187300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>123500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>164200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>154800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>180200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>137800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>136000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>87500</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>120400</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>91800</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>102100</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>98100</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>146200</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>94200</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>97000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>19600</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>60800</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>83900</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>97100</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>79400</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>87100</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>77600</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>89900</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>87500</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>79900</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>66700</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>63600</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>62800</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>54800</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>51000</v>
       </c>
-      <c r="AP35" s="3">
+      <c r="AQ35" s="3">
         <v>49500</v>
       </c>
     </row>
-    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43738</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43646</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43555</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43465</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43373</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43190</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43100</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>43008</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42916</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42825</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42735</v>
       </c>
-      <c r="AP38" s="2">
+      <c r="AQ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4175,8 +4260,9 @@
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
       <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4219,297 +4305,304 @@
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
       <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>595900</v>
+      </c>
+      <c r="E41" s="3">
         <v>543700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>467900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>565500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>695600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>616300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>458500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>731100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>415500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>379900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>423500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>418100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>513900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>446000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>490900</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>489600</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>498900</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>462500</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>411200</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>462200</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>435000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>426300</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>322400</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>308600</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>345000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>349100</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>286200</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>448800</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>300900</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>270800</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>392100</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>279900</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>304600</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>231400</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>277500</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>251900</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>296100</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>214100</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>267200</v>
       </c>
-      <c r="AP41" s="3">
+      <c r="AQ41" s="3">
         <v>242800</v>
       </c>
     </row>
-    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>3703700</v>
+      </c>
+      <c r="E42" s="3">
         <v>3204500</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>3360200</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>3631400</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>4790700</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>4442500</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>4613900</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>3907300</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>3072300</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>2392500</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>2364800</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>2773900</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>2461500</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>1837700</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>2579000</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>4505800</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>4195900</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>5184000</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>6541700</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>5701000</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>5152100</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>3815000</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>5272100</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>4247900</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>4441100</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>2335300</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>2548700</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>2631500</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>1806000</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>1971400</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>1460600</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>1473400</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>1551000</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>1315700</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AL42" s="3">
         <v>1366600</v>
       </c>
-      <c r="AL42" s="3">
+      <c r="AM42" s="3">
         <v>1500400</v>
       </c>
-      <c r="AM42" s="3">
+      <c r="AN42" s="3">
         <v>1285700</v>
       </c>
-      <c r="AN42" s="3">
+      <c r="AO42" s="3">
         <v>1245400</v>
       </c>
-      <c r="AO42" s="3">
+      <c r="AP42" s="3">
         <v>1248200</v>
       </c>
-      <c r="AP42" s="3">
+      <c r="AQ42" s="3">
         <v>1067300</v>
       </c>
     </row>
-    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E43" s="3">
+      <c r="E43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F43" s="3">
         <v>849800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>978200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>240000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>463000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>31600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>567700</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>13700</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>13400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>716500</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>14000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>15700</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>955800</v>
       </c>
-      <c r="Q43" s="3">
-        <v>0</v>
-      </c>
       <c r="R43" s="3">
         <v>0</v>
       </c>
@@ -4585,53 +4678,56 @@
       <c r="AP43" s="3">
         <v>0</v>
       </c>
+      <c r="AQ43" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>15900</v>
+      </c>
+      <c r="E44" s="3">
         <v>17400</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>20800</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>24800</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>23600</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>22600</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>23100</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>13700</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>19700</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>14500</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>13300</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>14100</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>11600</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>9400</v>
       </c>
-      <c r="Q44" s="3">
-        <v>0</v>
-      </c>
       <c r="R44" s="3">
         <v>0</v>
       </c>
@@ -4707,53 +4803,56 @@
       <c r="AP44" s="3">
         <v>0</v>
       </c>
+      <c r="AQ44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>336700</v>
+      </c>
+      <c r="E45" s="3">
         <v>326000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>312200</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>342400</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>341300</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>335400</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>332800</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>351500</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>1140400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>307800</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>304500</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>290900</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>267300</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>245100</v>
       </c>
-      <c r="Q45" s="3">
-        <v>0</v>
-      </c>
       <c r="R45" s="3">
         <v>0</v>
       </c>
@@ -4829,53 +4928,56 @@
       <c r="AP45" s="3">
         <v>0</v>
       </c>
+      <c r="AQ45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>5059600</v>
+      </c>
+      <c r="E46" s="3">
         <v>4475100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>5351800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>5876200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>6390800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>6196600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>5791100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>6032300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>5073500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>3448000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>4115200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>3815900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>3608700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>3796400</v>
       </c>
-      <c r="Q46" s="3">
-        <v>0</v>
-      </c>
       <c r="R46" s="3">
         <v>0</v>
       </c>
@@ -4951,53 +5053,56 @@
       <c r="AP46" s="3">
         <v>0</v>
       </c>
+      <c r="AQ46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>11215100</v>
+      </c>
+      <c r="E47" s="3">
         <v>10939600</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>10004300</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>9126500</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>9010400</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>8405000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>8316700</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>8046000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>8517200</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>8605200</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>7764100</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>7917400</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>7421700</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>7275600</v>
       </c>
-      <c r="Q47" s="3">
-        <v>0</v>
-      </c>
       <c r="R47" s="3">
         <v>0</v>
       </c>
@@ -5073,252 +5178,261 @@
       <c r="AP47" s="3">
         <v>0</v>
       </c>
+      <c r="AQ47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>779000</v>
+      </c>
+      <c r="E48" s="3">
         <v>777600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>781600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>775400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>776300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>776700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>779100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>772000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>722300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>744800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>749000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>747500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>749400</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>760300</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>764800</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>763000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>762400</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>761200</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>766400</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>748900</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>752400</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>760500</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>768800</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>774300</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>769900</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>764600</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>920000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>882800</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>874300</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>841800</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>671200</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>664500</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>639300</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>626700</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>621900</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>610000</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>605200</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>598700</v>
-      </c>
-      <c r="AO48" s="3">
-        <v>597300</v>
       </c>
       <c r="AP48" s="3">
         <v>597300</v>
       </c>
+      <c r="AQ48" s="3">
+        <v>597300</v>
+      </c>
     </row>
-    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1087200</v>
+      </c>
+      <c r="E49" s="3">
         <v>1086000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1091000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1093900</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1101700</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1109300</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1122400</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1111000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>881200</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>879000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>872000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>890900</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>883000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>899000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>675700</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>676700</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>679800</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>682100</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>683500</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>675900</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>678300</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>680100</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>681700</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>683300</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>685600</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>687600</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>692300</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>628000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>631500</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>620200</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>622600</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>564900</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>531400</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>533900</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>519500</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>520700</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>519800</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>520000</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>520400</v>
       </c>
-      <c r="AP49" s="3">
+      <c r="AQ49" s="3">
         <v>506700</v>
       </c>
     </row>
-    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5439,8 +5553,11 @@
       <c r="AP50" s="3">
         <v>0</v>
       </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5561,53 +5678,56 @@
       <c r="AP51" s="3">
         <v>0</v>
       </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>911500</v>
+      </c>
+      <c r="E52" s="3">
         <v>835800</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>826900</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>779700</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>764200</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>771800</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>901000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>849800</v>
       </c>
-      <c r="K52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L52" s="3">
+      <c r="L52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M52" s="3">
         <v>734300</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>690700</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>777400</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>628000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>608400</v>
       </c>
-      <c r="Q52" s="3">
-        <v>0</v>
-      </c>
       <c r="R52" s="3">
         <v>0</v>
       </c>
@@ -5683,8 +5803,11 @@
       <c r="AP52" s="3">
         <v>0</v>
       </c>
+      <c r="AQ52" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5805,130 +5928,136 @@
       <c r="AP53" s="3">
         <v>0</v>
       </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>74668100</v>
+      </c>
+      <c r="E54" s="3">
         <v>72157400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>71142000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>69629600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>68983300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>65870100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>64879700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>63788400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>59781500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>57576900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>56259900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>55555200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>54286200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>52873500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>52949600</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>52382900</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>50969300</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>50250700</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>50142100</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>47832300</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>46738500</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>45682200</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>45080800</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>43731700</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>43540000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>38799800</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>36620600</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>34911900</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>33641800</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>32358600</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>31244800</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>30142700</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>29464600</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>28456800</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>27916000</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>27358200</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>26929300</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>25778900</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>25668600</v>
       </c>
-      <c r="AP54" s="3">
+      <c r="AQ54" s="3">
         <v>25321800</v>
       </c>
     </row>
-    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5971,8 +6100,9 @@
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
       <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -6015,175 +6145,179 @@
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
       <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>61141300</v>
+      </c>
+      <c r="E57" s="3">
         <v>58914400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>57717200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>56711400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>55816800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>53570000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>52512300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>51405000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>48049000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>46448900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>45397200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>44992700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>44038700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>42718200</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1645300</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1492300</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1307300</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1123400</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1120600</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>1031800</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>1145000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>1119700</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>1434700</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>1387400</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>1471100</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>1285700</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>841900</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>794200</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>798400</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>643700</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>669600</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>664900</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>676800</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>591400</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>537200</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>440900</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>495500</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>424500</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>505500</v>
       </c>
-      <c r="AP57" s="3">
+      <c r="AQ57" s="3">
         <v>446100</v>
       </c>
     </row>
-    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>140100</v>
+      </c>
+      <c r="E58" s="3">
         <v>118900</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>556500</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>141700</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>161400</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>181200</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>241800</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>199300</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>317700</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>335200</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>306100</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>472900</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>408900</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>284600</v>
       </c>
-      <c r="Q58" s="3">
-        <v>0</v>
-      </c>
       <c r="R58" s="3">
         <v>0</v>
       </c>
@@ -6259,8 +6393,11 @@
       <c r="AP58" s="3">
         <v>0</v>
       </c>
+      <c r="AQ58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -6303,8 +6440,8 @@
       <c r="P59" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q59" s="3">
-        <v>0</v>
+      <c r="Q59" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R59" s="3">
         <v>0</v>
@@ -6336,24 +6473,24 @@
       <c r="AA59" s="3">
         <v>0</v>
       </c>
-      <c r="AB59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC59" s="3">
+      <c r="AB59" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD59" s="3">
         <v>197600</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>192100</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>195100</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>196900</v>
       </c>
-      <c r="AG59" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AH59" s="3" t="s">
         <v>5</v>
       </c>
@@ -6363,8 +6500,8 @@
       <c r="AJ59" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AK59" s="3">
-        <v>0</v>
+      <c r="AK59" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AL59" s="3">
         <v>0</v>
@@ -6381,53 +6518,56 @@
       <c r="AP59" s="3">
         <v>0</v>
       </c>
+      <c r="AQ59" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>61334900</v>
+      </c>
+      <c r="E60" s="3">
         <v>60435100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>58336500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>56922500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>56035700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>53811400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>52802500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>51679600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>48433100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>46849000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>45754400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>45520000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>44493000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>43044800</v>
       </c>
-      <c r="Q60" s="3">
-        <v>0</v>
-      </c>
       <c r="R60" s="3">
         <v>0</v>
       </c>
@@ -6503,175 +6643,181 @@
       <c r="AP60" s="3">
         <v>0</v>
       </c>
+      <c r="AQ60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>4373800</v>
+      </c>
+      <c r="E61" s="3">
         <v>4344200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>4191500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>4282700</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>4328700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>4232500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>4238000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>4370100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>4334600</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>3932800</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>3624400</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>3647200</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>3364700</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>3580600</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>1270000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>1128800</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>1157100</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>1157200</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>1175400</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>1180900</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>1208800</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>1194600</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>1197600</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>1189400</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>1189900</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>1165100</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>1087300</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>1090400</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>1097500</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>748800</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>786600</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>748900</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>627000</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>621800</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>658800</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>624300</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>624000</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>392600</v>
-      </c>
-      <c r="AO61" s="3">
-        <v>392500</v>
       </c>
       <c r="AP61" s="3">
         <v>392500</v>
       </c>
+      <c r="AQ61" s="3">
+        <v>392500</v>
+      </c>
     </row>
-    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E62" s="3">
+      <c r="D62" s="3">
+        <v>1434300</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F62" s="3">
         <v>1352600</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>1378600</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>1393200</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>1225700</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>1493600</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>1339000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1477300</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>1358700</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>1480900</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>1372500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>1386500</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>1232700</v>
       </c>
-      <c r="Q62" s="3">
-        <v>0</v>
-      </c>
       <c r="R62" s="3">
         <v>0</v>
       </c>
@@ -6747,8 +6893,11 @@
       <c r="AP62" s="3">
         <v>0</v>
       </c>
+      <c r="AQ62" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6869,8 +7018,11 @@
       <c r="AP63" s="3">
         <v>0</v>
       </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6991,8 +7143,11 @@
       <c r="AP64" s="3">
         <v>0</v>
       </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -7113,130 +7268,136 @@
       <c r="AP65" s="3">
         <v>0</v>
       </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>67143000</v>
+      </c>
+      <c r="E66" s="3">
         <v>64779300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>63883300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>62583900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>61757600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>59269500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>58535400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>57388700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>54244900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>52140500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>50860400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>50539600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>49244300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>47858000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>48152800</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>47745000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>46241700</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>45758400</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>45643500</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>43422000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>42399400</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>41429700</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>40964800</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>39657600</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>39549800</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>35099500</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>32929300</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>31371600</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>30194800</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>28986600</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>27977300</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>26962900</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>26357700</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>25425500</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>24939000</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>24449200</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>24089800</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>23013900</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>22972900</v>
       </c>
-      <c r="AP66" s="3">
+      <c r="AQ66" s="3">
         <v>22647300</v>
       </c>
     </row>
-    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7279,8 +7440,9 @@
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
       <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7401,8 +7563,11 @@
       <c r="AP68" s="3">
         <v>0</v>
       </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7523,8 +7688,11 @@
       <c r="AP69" s="3">
         <v>0</v>
       </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7538,10 +7706,10 @@
         <v>425000</v>
       </c>
       <c r="G70" s="3">
+        <v>425000</v>
+      </c>
+      <c r="H70" s="3">
         <v>837500</v>
-      </c>
-      <c r="H70" s="3">
-        <v>412500</v>
       </c>
       <c r="I70" s="3">
         <v>412500</v>
@@ -7601,7 +7769,7 @@
         <v>412500</v>
       </c>
       <c r="AB70" s="3">
-        <v>125000</v>
+        <v>412500</v>
       </c>
       <c r="AC70" s="3">
         <v>125000</v>
@@ -7637,7 +7805,7 @@
         <v>125000</v>
       </c>
       <c r="AN70" s="3">
-        <v>251300</v>
+        <v>125000</v>
       </c>
       <c r="AO70" s="3">
         <v>251300</v>
@@ -7645,8 +7813,11 @@
       <c r="AP70" s="3">
         <v>251300</v>
       </c>
+      <c r="AQ70" s="3">
+        <v>251300</v>
+      </c>
     </row>
-    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7767,130 +7938,136 @@
       <c r="AP71" s="3">
         <v>0</v>
       </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>4907800</v>
+      </c>
+      <c r="E72" s="3">
         <v>4719600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>4537500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>4356400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>4200900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>4045900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>3897200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>3748700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>3615600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>3498500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>3345400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>3253300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>3120600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>2997300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>2849000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>2731800</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>2616500</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>2548500</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>2447500</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>2373400</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>2289000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>2208500</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>2080000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>2001900</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>1921000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>1917600</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>1899600</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>1830200</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>1747300</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>1682000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>1610600</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>1543700</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>1464500</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>1387700</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>1313700</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>1254800</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>1199000</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>1143900</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>1096500</v>
       </c>
-      <c r="AP72" s="3">
+      <c r="AQ72" s="3">
         <v>1051700</v>
       </c>
     </row>
-    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -8011,8 +8188,11 @@
       <c r="AP73" s="3">
         <v>0</v>
       </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -8133,8 +8313,11 @@
       <c r="AP74" s="3">
         <v>0</v>
       </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8255,130 +8438,136 @@
       <c r="AP75" s="3">
         <v>0</v>
       </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>7100100</v>
+      </c>
+      <c r="E76" s="3">
         <v>6953100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>6833700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>6620800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>6388200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>6188000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>5931800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>5987200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>5124100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>5023900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>4987000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>4603100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>4629400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>4603000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>4384300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>4225500</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>4315100</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>4079800</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>4086200</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>3997800</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>3926500</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>3840000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>3703500</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>3661600</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>3577700</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>3575400</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>3566300</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>3415300</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>3322000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>3247000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>3142600</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>3054800</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>2981900</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>2906300</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>2851900</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>2783900</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>2714500</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>2513700</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>2444400</v>
       </c>
-      <c r="AP76" s="3">
+      <c r="AQ76" s="3">
         <v>2423200</v>
       </c>
     </row>
-    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8499,257 +8688,266 @@
       <c r="AP77" s="3">
         <v>0</v>
       </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43738</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43646</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43555</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43465</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43373</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43190</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43100</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>43008</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42916</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42825</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42735</v>
       </c>
-      <c r="AP80" s="2">
+      <c r="AQ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>233700</v>
+      </c>
+      <c r="E81" s="3">
         <v>227400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>223000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>216300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>195500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>189000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>185400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>170000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>152400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>187300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>123500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>164200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>154800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>180200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>137800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>136000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>87500</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>120400</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>91800</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>102100</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>98100</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>146200</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>94200</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>97000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>19600</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>60800</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>83900</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>97100</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>79400</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>87100</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>77600</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>89900</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>87500</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>79900</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>66700</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>63600</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>62800</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>54800</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>51000</v>
       </c>
-      <c r="AP81" s="3">
+      <c r="AQ81" s="3">
         <v>49500</v>
       </c>
     </row>
-    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8792,130 +8990,134 @@
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
       <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>14500</v>
+      </c>
+      <c r="E83" s="3">
         <v>13400</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>13200</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>11200</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>11700</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>9600</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>10100</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>14200</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>4800</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>7800</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>5800</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>8600</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>10300</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>13200</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>17300</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>19500</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>20700</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>24500</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>26400</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>23900</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>25900</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>25600</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>25100</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>24200</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>23800</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>23400</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>23500</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>21500</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>22100</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>21200</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>18800</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>16900</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>16100</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>15900</v>
-      </c>
-      <c r="AK83" s="3">
-        <v>16600</v>
       </c>
       <c r="AL83" s="3">
         <v>16600</v>
       </c>
       <c r="AM83" s="3">
+        <v>16600</v>
+      </c>
+      <c r="AN83" s="3">
         <v>15500</v>
-      </c>
-      <c r="AN83" s="3">
-        <v>14400</v>
       </c>
       <c r="AO83" s="3">
         <v>14400</v>
       </c>
       <c r="AP83" s="3">
+        <v>14400</v>
+      </c>
+      <c r="AQ83" s="3">
         <v>11500</v>
       </c>
     </row>
-    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -9036,8 +9238,11 @@
       <c r="AP84" s="3">
         <v>0</v>
       </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -9158,8 +9363,11 @@
       <c r="AP85" s="3">
         <v>0</v>
       </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9280,8 +9488,11 @@
       <c r="AP86" s="3">
         <v>0</v>
       </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9402,8 +9613,11 @@
       <c r="AP87" s="3">
         <v>0</v>
       </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9524,130 +9738,136 @@
       <c r="AP88" s="3">
         <v>0</v>
       </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>255100</v>
+      </c>
+      <c r="E89" s="3">
         <v>927200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>251700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>209800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>329200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>119800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>490800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-61600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>221200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>71100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>247900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>88300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>339800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>68400</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>319800</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>231800</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>365300</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>458000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>399900</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>82200</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>432000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>216800</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-95300</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-53500</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>10100</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-379800</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>288900</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-45200</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-65500</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>87700</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>116100</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>158400</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>80400</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>22400</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>252700</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>23200</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>-3900</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>129700</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>392600</v>
       </c>
-      <c r="AP89" s="3">
+      <c r="AQ89" s="3">
         <v>9800</v>
       </c>
     </row>
-    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9690,130 +9910,134 @@
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
       <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-17300</v>
+      </c>
+      <c r="E91" s="3">
         <v>-13200</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-23000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-17200</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-9700</v>
       </c>
-      <c r="H91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I91" s="3">
+      <c r="I91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J91" s="3">
         <v>-19600</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-16700</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-39200</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-10600</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-17200</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-19900</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-200</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-9100</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-16000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-14100</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-15600</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-7700</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-33600</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-11300</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-7700</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-4400</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-9300</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-16300</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-16700</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-21400</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-30600</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-20200</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-17700</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-13600</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-15600</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-20300</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-20700</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-11600</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-19600</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-13300</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-15400</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-10800</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-11300</v>
       </c>
-      <c r="AP91" s="3">
+      <c r="AQ91" s="3">
         <v>-8100</v>
       </c>
     </row>
-    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9934,8 +10158,11 @@
       <c r="AP92" s="3">
         <v>0</v>
       </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -10056,130 +10283,136 @@
       <c r="AP93" s="3">
         <v>0</v>
       </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-2423300</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1867000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-1507600</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-740000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-2947700</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-973400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-1718400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-663400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-2145400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-1419200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-609700</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-1396500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-1346000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>114400</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-542200</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-1555500</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-899300</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-493800</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-2562100</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-1164000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-1347000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-855700</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-1064300</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-140600</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-4528600</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-1448900</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-1229800</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-978900</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-778700</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-1031600</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-847800</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-569900</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-846900</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-498900</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-615400</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-467900</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-913600</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-306300</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>-480400</v>
       </c>
-      <c r="AP94" s="3">
+      <c r="AQ94" s="3">
         <v>-953700</v>
       </c>
     </row>
-    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -10222,16 +10455,17 @@
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
       <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>37100</v>
+      </c>
+      <c r="E96" s="3">
         <v>37000</v>
-      </c>
-      <c r="E96" s="3">
-        <v>33500</v>
       </c>
       <c r="F96" s="3">
         <v>33500</v>
@@ -10240,46 +10474,46 @@
         <v>33500</v>
       </c>
       <c r="H96" s="3">
+        <v>33500</v>
+      </c>
+      <c r="I96" s="3">
         <v>33400</v>
-      </c>
-      <c r="I96" s="3">
-        <v>29900</v>
       </c>
       <c r="J96" s="3">
         <v>29900</v>
       </c>
       <c r="K96" s="3">
+        <v>29900</v>
+      </c>
+      <c r="L96" s="3">
         <v>28300</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>27200</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>24400</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>24500</v>
-      </c>
-      <c r="O96" s="3">
-        <v>24400</v>
       </c>
       <c r="P96" s="3">
         <v>24400</v>
       </c>
       <c r="Q96" s="3">
+        <v>24400</v>
+      </c>
+      <c r="R96" s="3">
         <v>-27700</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-28500</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-25600</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-26500</v>
-      </c>
-      <c r="U96" s="3">
-        <v>-24700</v>
       </c>
       <c r="V96" s="3">
         <v>-24700</v>
@@ -10288,25 +10522,25 @@
         <v>-24700</v>
       </c>
       <c r="X96" s="3">
+        <v>-24700</v>
+      </c>
+      <c r="Y96" s="3">
         <v>-24600</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-23100</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-26400</v>
-      </c>
-      <c r="AA96" s="3">
-        <v>-18200</v>
       </c>
       <c r="AB96" s="3">
         <v>-18200</v>
       </c>
       <c r="AC96" s="3">
+        <v>-18200</v>
+      </c>
+      <c r="AD96" s="3">
         <v>-16500</v>
-      </c>
-      <c r="AD96" s="3">
-        <v>-16200</v>
       </c>
       <c r="AE96" s="3">
         <v>-16200</v>
@@ -10315,37 +10549,40 @@
         <v>-16200</v>
       </c>
       <c r="AG96" s="3">
-        <v>-12800</v>
+        <v>-16200</v>
       </c>
       <c r="AH96" s="3">
         <v>-12800</v>
       </c>
       <c r="AI96" s="3">
-        <v>-12700</v>
+        <v>-12800</v>
       </c>
       <c r="AJ96" s="3">
         <v>-12700</v>
       </c>
       <c r="AK96" s="3">
-        <v>-9900</v>
+        <v>-12700</v>
       </c>
       <c r="AL96" s="3">
         <v>-9900</v>
       </c>
       <c r="AM96" s="3">
+        <v>-9900</v>
+      </c>
+      <c r="AN96" s="3">
         <v>-9800</v>
       </c>
-      <c r="AN96" s="3">
+      <c r="AO96" s="3">
         <v>-11000</v>
-      </c>
-      <c r="AO96" s="3">
-        <v>-9800</v>
       </c>
       <c r="AP96" s="3">
         <v>-9800</v>
       </c>
+      <c r="AQ96" s="3">
+        <v>-9800</v>
+      </c>
     </row>
-    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10466,8 +10703,11 @@
       <c r="AP97" s="3">
         <v>0</v>
       </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10588,8 +10828,11 @@
       <c r="AP98" s="3">
         <v>0</v>
       </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10710,130 +10953,136 @@
       <c r="AP99" s="3">
         <v>0</v>
       </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>2220300</v>
+      </c>
+      <c r="E100" s="3">
         <v>1015600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>1158400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>400100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>2697800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>1011400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>955000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>1040600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>1959800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>1304500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>367100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>1212400</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>1074200</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-227800</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>223600</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>1314300</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>570400</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>87200</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>2111200</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>1109100</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>923600</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>742800</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>1173400</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>157700</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>4514100</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>1891600</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>778500</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>1171900</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>874300</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>822500</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>843900</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>386400</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>840000</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>430500</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>388400</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>400500</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>997600</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>123700</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>111400</v>
       </c>
-      <c r="AP100" s="3">
+      <c r="AQ100" s="3">
         <v>919500</v>
       </c>
     </row>
-    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -10876,8 +11125,8 @@
       <c r="P101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q101" s="3">
-        <v>0</v>
+      <c r="Q101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R101" s="3">
         <v>0</v>
@@ -10954,126 +11203,132 @@
       <c r="AP101" s="3">
         <v>0</v>
       </c>
+      <c r="AQ101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>52100</v>
+      </c>
+      <c r="E102" s="3">
         <v>75800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-97500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-130100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>79300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>157700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-272600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>315600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>35600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-43600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>5300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-95800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>67900</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-45000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>1300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-9300</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>36400</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>51400</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-51100</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>27300</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>8600</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>103900</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>13800</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-36400</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-4400</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>63000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-162300</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>147800</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>30200</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-121400</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>112200</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-24600</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>73200</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-46100</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>25600</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>-44200</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>79000</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>-52900</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>23100</v>
       </c>
-      <c r="AP102" s="3">
+      <c r="AQ102" s="3">
         <v>-24600</v>
       </c>
     </row>
